--- a/web_controlled_48_relay/BOM.xlsx
+++ b/web_controlled_48_relay/BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -41,12 +41,6 @@
   </si>
   <si>
     <t xml:space="preserve">Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5*3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAM</t>
   </si>
   <si>
     <t xml:space="preserve">**</t>
@@ -125,7 +119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="20">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -171,84 +165,35 @@
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium"/>
       <right style="thin"/>
-      <top style="medium"/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
-      <top style="medium"/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
-      <top style="medium"/>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top/>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -341,7 +286,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -386,7 +331,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -402,67 +363,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -483,8 +400,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="10.51171875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G1048576"/>
+  <sheetFormatPr defaultColWidth="10.51953125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -518,164 +435,112 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="16" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16" t="s">
+      <c r="C3" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <f aca="false">C3*D3</f>
+        <v>175</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
+      <c r="C4" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <f aca="false">C4*D4</f>
+        <v>360</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="E5" s="8"/>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="C6" s="13" t="n">
+        <v>2365</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <f aca="false">C9*D9</f>
-        <v>175</v>
-      </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="14"/>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="E6" s="14" t="n">
+        <f aca="false">C6*D6</f>
+        <v>2365</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+      <c r="B8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <f aca="false">C11*D11</f>
-        <v>2000</v>
-      </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="2" t="n">
-        <f aca="false">SUM(E2:E12)</f>
-        <v>2175</v>
-      </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30"/>
-    </row>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="2" t="n">
+        <f aca="false">SUM(E2:E7)</f>
+        <v>2900</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
